--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2955,6 +2955,60 @@
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-07-19 ("cashflow. Approve.")</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Income pop-up (v2): "Which 12 months are you entering?" — Calendar year N or Next 12 months; every month chip and editor carries month + year (incl. across the New-Year boundary); both frames write the same canonical calendar slots; note "this yearly pattern repeats". Receipt scanning: totals never read from payment-mechanics lines.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Founder Build-44 findings (rows 33-34)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Founder — directed 2026-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Spending tab conformance: month header with the sum, recent rows with source chips (by hand / imported; bank arrives with Teller), categories-vs-plan card, All-transactions and Import doors opening the proven full bodies; day-one three doors.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Founder Build-44 finding (row 40) — conform to the approved mock</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Approved mock is the spec</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3009,6 +3009,195 @@
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Approved mock is the spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Empty-state odds strip RESOLVED: the locked Sample gauge ("Sample: 84% to age 92") is the approved empty state. The later 3-questions-invite mock is retired.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Two approvals conflicted by date (Jul-15 gauge vs later mock); the July-24 audit surfaced it; founder picked the gauge.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Founder — DECIDED 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Net worth / Connect / Settings</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Disconnect promise UNIFIED: on disconnect the user is offered the choice — keep the numbers as a by-hand account, or delete the connection’s data. Consent copy, Settings, and the future account-page door all state this same promise. Exact copy rides the Build-46 item walk for approval.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Doc said "numbers stay", shipped consent said "we delete" — behavior in Settings already offered the choice; founder aligned the promise to the choice.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Founder — DECIDED 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Emergency-cushion card ("X months of essentials", below the fold) REINSTATED as to-build: it returns to scope, mock first — founder approves the drawn Net worth screen before any code.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Doc specified it; v7 FINAL mock dropped it; the July-24 audit put the drop-or-build call to the founder, who chose build.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Founder — DECIDED 2026-07-28 (build after mock approval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Type-size question CLOSED: dense tables (Invest winners/laggards, holdings list) keep their approved compact sizes; the 17-point money floor applies to heroes and standalone money only.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Long-open decision (17pt floor vs dense tables); the approved v7 tables set the precedent; founder confirmed.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Founder — DECIDED 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Screen inventory</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Legacy modules (Estate, Insurance, Tax organizer, Job safety, Credit) STAY in the v1 launch. They remain rows in the 97-row launch sign-off walk and must each pass it.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Not covered by FCC docs; audit asked keep-vs-hide; founder chose keep for launch value.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Founder — DECIDED 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chart colors: the UX doc’s validated colorblind-safe palettes WILL BE ADOPTED app-wide (one consistent set; e.g. Cash gets one color everywhere). Recolored mocks of every affected chart come first; nothing changes until the founder approves the pictures.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shipped colors drifted between screens and the validated palettes were never adopted; colorblind-safe is a stated UX standard.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Founder — DECIDED 2026-07-28 (adopt after mock approval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>STANDING RULE ADOPTED: every founder approval gets a dated row in this Changelog tab the same day, alongside the mock. Also recorded in the repo’s CLAUDE.md.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Root cause of doc-vs-code drift found by the July-24 audit: dozens of July approvals, 4 changelog rows.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Founder — ADOPTED 2026-07-28</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3198,6 +3198,60 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>Founder — ADOPTED 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUILD-46 PAYLOAD BUILT — all 16 walk rows approved verbally ("build all 16") and coded with pinning tests: Social-Security odds use the claim-age-adjusted check on every surface; unpriced holdings show what-you-paid; insights pop-up masks; bond/alt sales write SELL ledger rows; one shared market-average formula; equity vests land in their months on every view; Net worth gains the path-ahead row and the By class/institution/type pills (v7 FINAL); dollar-first insight wording; acronyms spelled out; one estimate tag + one trying-it-out sentence; 44pt tap-target fixes with ratchet; paycheck-card wording; spoken labels say "hidden" (class-fixed with guard); one offer-the-choice disconnect promise. Suite 1,270 → 1,289 green.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Founder approval 2026-07-29 (Build-46 walk, all rows)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Invest</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nest-egg info-dot spec updated to the founder’s approved copy (2026-07-19) — the doc still carried the pre-approval wording; the app was already correct (hand-verified in git).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>July-24 audit item 32 resolved as doc-stale, not code-drift</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Doc correction — evidence in git history</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12354,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Both open the SAME plain-English explanation of the estimate: earmarked accounts grown yearly at the mix's market yardstick until retirement age; each year's savings added with the growth it has time to earn; delta = the difference the extra monthly amount makes. Notes that growth basis/inflation/inputs are changeable in Plan; "an estimate, not a promise".</t>
+          <t>Both open the SAME plain-English explanation (the founder’s own approved copy, 2026-07-19): “We take your earmarked retirement accounts and apply benchmark market growth tailored to your specific asset mix, compounding your current balances and future contributions through your retirement date. The amount shown represents the incremental wealth generated by this additional monthly contribution over that period. As always, you have full control over return assumptions, inflation rates, and variables in Plan. An estimate, not a promise.”</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3252,6 +3252,33 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>Doc correction — evidence in git history</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUILD-47 WALK BUILT — all 25 rows approved verbally ("Approve all 25") and coded with pins: HSA honest cap · SS claim-NOW at 68-69 · RMD card taken-check · value-as-of in bond/alt editors · undated-value nudge · rothConversionCost canonical · capacity derived from surplusByMonth · sourceWording shared · RMD schedule on the shared growth step · snapshot reads blendedReturn · HeroAmount (5 heroes) · hidden-balances banner ×5 tabs · pull-to-refresh · approved door lines · Roth banner+save+dated hub to-do · period sync · tappable concentration · double-fire suppression · possible_duplicate flag (incl. manual) · Reduce Motion ×19 modal files · component spoken label · shared picker naming · confirm-before-remove · plain income note+door · add-any-income-source. Plus B46 findings 7/8/10 accuracy fixes. Suite 1,289 → 1,311.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Founder approval 2026-07-30 (Build-47 walk, all rows)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-07-30</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3279,6 +3279,33 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VALIDATED COLOR PALETTES ADOPTED (founder YES on chart-palettes-v2 FINAL): ChartPalette + ClassMarkColors moved to the UX doc's colorblind-validated fixed-order set (#2a78d6 stocks · #1baf7a cash · #eda100 real estate · #4a3aa7 bonds · #eb6834 alternatives · #e87ba4 personal · #898781 mixed); successGreen marks → the validated good step #0ca30c. Colors ONLY — layouts/words/numbers unchanged per the mock's stated rule. Exact values pinned by test.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UX doc Color tab (validated set was specified, never adopted); founder approval 2026-07-30</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-07-30 ("yes")</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3306,6 +3306,33 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-07-30 ("yes")</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Home · Net worth</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>STALENESS STAMPS BUILT (mock #4 approved with founder change): when a connected account is 3+ days old, the Home hero and Net worth hero carry one amber line inside the box — "⏱ &lt;institution&gt; part as of &lt;date&gt; — N days old · pull to refresh" — left-justified like their sibling lines. The standalone stale line now serves the retired lens only (its hero has no investments box).</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Founder approval 2026-07-31 with the left-justified change; mock v2 = as-built record</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-07-31</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3331,6 +3331,33 @@
         </is>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NW · Invest · Home · app-wide</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MOCK-BATCH VERDICT ROUND BUILT: separator dots = the DARKER designed glyph (founder pick C — visibility for 55-70 eyes; Colors.sepDot token + DotJoined on marquee lines) · source chips on NW rows (approved) · cushion card (approved; 3 states) · matured-bond banner (approved; paid-out writes the ledger) · add/record ROUTER (findings 3+6; chips open the real editors with separate fields, Record gains bond/alt doors) · path-ahead row stays its own card + gains the how-ⓘ (nestEggMath) · "See your growth" KEPT as-is · staleness stamps in-hero, left-justified · sentence periods stay (founder call). Suite 1,319 green.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Founder verdicts 2026-07-31 in chat</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-07-31</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3358,6 +3358,33 @@
         </is>
       </c>
       <c r="E18" t="inlineStr">
+        <is>
+          <t>Founder — APPROVED 2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Home · app root · Invest sheets</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LOADING/OFFLINE DECIDED+BUILT: couldn't-refresh banner on Home (store-flagged, honest as-of, clears on success); the mock's grey-bar skeleton REJECTED by founder question and replaced by the root hydration hold (no screen renders before the store is ready — sub-second, kills the cold-start doors-flash). Router mock v2 delivered per founder revision (drawn from the shipping editors, separate fields).</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Founder verdicts 2026-07-31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-07-31</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3387,6 +3387,33 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>Founder — APPROVED 2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Income (equity editor)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B47 WALK FINDINGS 1-2 FIXED: equity editor gains the company stock symbol field (live price seeds new rows, editable; full re-marking joins the provider work) and a real bottom Done button (the top-bar link was invisible from a long form; "saves as you type" note).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Founder Build-47 walk findings, 2026-07-31</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Founder findings — fixed same hour</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3414,6 +3414,33 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>Founder findings — fixed same hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Connected accounts (ingest)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B47 FINDING 3 FIXED (Vanguard): balance authority rule gains the derive-from-holdings fallback when the broker reports no usable total (missing/zero) — marks + options + cash sleeve; USD-only (currency guard); empty stays zero; real totals still win. 3 new ingest pins.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Founder Build-47 walk (second live institution)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Founder finding — fixed same hour</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3441,6 +3441,33 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>Founder finding — fixed same hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cash flow / Net worth — debts</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ONE debt editor shaped by repayment (installment: real payment ↔ paid-off-by; cards: min + you-pay; due in full: amount + date → dated big-ticket in cash flow + bill calendar). Replaces the two drifted debt forms.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>B47 walk finding 11: mortgage end year + actual payment were never asked; a loan due in full on a date was unrepresentable. Mock debt-editor-v1-2026-07-31 approved.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Founder (chat, "approved.")</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3468,6 +3468,33 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>Founder (chat, "approved.")</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Retirement — Where you stand</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Coasting box copy: each state one sentence ("today's $X alone gets there by N" / "alone doesn't get there — even by 80"); "growing at %" wording</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>B47 walk finding 13: the three stacked fragments contradicted each other</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Founder (device finding; fix per plain-English rule)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3495,6 +3495,33 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>Founder (device finding; fix per plain-English rule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Invest — holding detail</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Full page rebuilt to mock v2: price hero + graph + period chips, position/compare/lots/dividends-realized/tax all in one table grammar; ✎ edit in header; unpriced = honest basis hero with 3-decimal averages</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B47 walk finding 6; mock holding-detail-full-v2-2026-07-31 approved</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Founder (chat, "holding screen - approved.")</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3522,6 +3522,33 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>Founder (chat, "holding screen - approved.")</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Net worth — By type view</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>All cash-bucket account types merge under one group header "Cash and cash equivalents" (was per-type headers, e.g. "Savings" covering CD + money market + cash)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B47 walk finding 14: founder — call it what it is</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3547,6 +3547,33 @@
         </is>
       </c>
       <c r="E25" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Plan hub (redesign in review)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Decision-row grammar: every row a complete first-person question — When can I retire? / Can I afford it? (founder dropped "all") / When should I claim Social Security? / Which account do I draw from first? / Is a Roth move worth it? / Can I spend more?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Founder verdict on mock v8 research round ("like it"); NN/g 65+ readability + industry best practice</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3574,6 +3574,60 @@
         </is>
       </c>
       <c r="E26" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Plan hub</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FULL REDESIGN BUILT to mock v9 (founder: "all mock up approved"): spectrum gauge verdicts w/ if-clause per lens, ONE dated next-decision card (required withdrawal &gt; SS window), retiree paycheck card = Home engine, dynamic first-day door counting only missing answers + crediting accounts, question-grammar rows ranked by mind-order, honest locks, fenced sandbox</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plan-tab redesign round, mocks v1→v9</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Plan hub</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>"What big costs are coming?" feature APPROVED; capture screen mocked (big-costs-v1) — builds on its approval; hub row lands with it</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>One-time future costs invisible to the long-range odds today</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3628,6 +3628,33 @@
         </is>
       </c>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Screen inventory</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orphan/legacy screens (income-detail, old income/invest/savings, Tips, Rewards) KEPT — reusable when building for other age groups; menu unchanged</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Founder decision on the primary-flows document</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3657,6 +3657,249 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Plan / big costs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>big-costs-v1 capture mock APPROVED — capture + simulation + hub row build into 48</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>All adoption surfaces</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ONE adopt verb: "Use as my plan" everywhere (sweep same day)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Invest / holding detail</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Look-back card KEPT on the holding page (mock omission was a drawing gap)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Plan / Social Security</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>"Remind me" at the claim window BUILDS into 48 (existing notification scaffolding)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Stress test · Insights · Tips</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Advice voice SOFTENED to fact-plus-choice on all three ("set this as a goal" class removed)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Menu (TopBar)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rewards, Tips, Build-credit tiles LEAVE the 55-70 menu; College planner + Estate stay; screens all kept in code</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Insights · Cash flow</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Goal-offtrack insight + "Add something else" link BUILD into 48; Invest return-breakdown goes MOCK-FIRST (next batch)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SS · multi-goal · Roth</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>STEPPERS stay (65+ precision); design sheet slider rows to be refreshed to match</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Paycheck card</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4%-guideline heads-up REWORDED to own-math framing ("above what your own numbers support long-term")</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pre-48 decision round</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3900,6 +3900,33 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Connect flow (F1)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PROVIDER PIVOT: SnapTrade OUT (founder saw connected financials displayed in its dashboard — privacy call), Plaid IN for beta. Migration = next workstream AFTER Build 48 (seam absorbs it: Plaid link swap, Investments ingest mapping, consent copy, disconnect/heal). NEW design-first feature unlocked: credit-card transaction import (Transactions + Liabilities products). Founder accepts one-time reconnect cost at LLC/launch re-setup.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Founder decision (checked SnapTrade dashboard)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3925,6 +3925,33 @@
         </is>
       </c>
       <c r="E39" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Connect flow (F1)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Provider pivot ON HOLD — founder evaluating Plaid vs SnapTrade vs Teller directly; no code or stack changes meanwhile</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Founder redirect same day</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3954,6 +3954,87 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Home (retroactive to 2026-07-16)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>+Expense floating button removed from Home — logging lives on Cash flow only (founder UX review 7/16; predates this changelog's start)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pre-48 audit B3: decision was never logged</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Founder (7/16 review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Section heading is "CHIEF OF STAFF — WHAT NEEDS YOU (n)" (founder 7/15 design round)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pre-48 audit B4: sheet row said the pre-round wording</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Founder (7/15 round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Plan · Invest · Cash flow · Net worth sheets</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SHEET REFRESH NOTE: hub rows superseded by mock v9; holding detail by holding-detail-full-v2; debt capture by debt-editor-v1; Cash-flow income by the one Add chooser; Net worth by-type by Cash-and-cash-equivalents. The changelog rows above are the current truth for these elements.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pre-48 audit B4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recorded by audit</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4035,6 +4035,33 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>Recorded by audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Invest</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Return breakdown BUILT to approved mock (Price change · Realized · Dividends · Interest under the period total; sparse-honest; ledger-only)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Design r16; founder "return breakdown - approved"</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4062,6 +4062,33 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>First-run setup</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>First bullet: "Everything you own and owe, in one place — accounts (investment, 401k, checking, savings), your home and other property, debts — one live view." (was "Map your whole money picture")</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>B48 walk finding 1 + founder second thought; matches the Net worth screen's Own − Owe language</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Founder (decision round)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4089,6 +4089,33 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>Founder (decision round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>First-run setup</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>First bullet FINAL: "All your assets and debts in one place" (founder's own wording, superseding the same-day own-and-owe pick)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>B48 walk finding 1, round 3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4116,6 +4116,33 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>First-run setup</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>First bullet CLOSED: "All your assets and debts in one place — accounts (investment, 401k, checking, savings), your home and other property, and every debt (mortgage, cards, loans) — one live view."</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>B48 finding 1 final round — complete-inventory principle + parallel examples</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Founder ("love it")</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4143,6 +4143,33 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>Founder ("love it")</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alternatives capture</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Private equity + Hedge funds OUT of phase 1 (founder: keep it simple) — capture chips trimmed on both editors; data model keeps the kinds so anything saved still renders</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Founder decision</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4170,6 +4170,33 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Navigation (all surfaces)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The Invest tab is renamed PERFORMANCE (founder pick: Net worth · Performance) — one TAB_META change sweeps the bottom bar, menu strip, and desktop sidebar; tab-name copy swept on 3 screens. Route keys unchanged.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Two tabs kept; names now say what-I-have vs how-it's-doing</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Founder (decision)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4197,6 +4197,33 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>Founder (decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BY TYPE view REMOVED (founder — resolves the open By-type question); WHAT YOU OWN restructures to the three uber-categories (Cash / Investments / Personal property) with classes as rows inside; two grouping pills remain: By category · By institution. Investments total = Performance total by definition (sweep cash under Cash).</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pair-mock rounds v2-v6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4222,6 +4222,33 @@
         </is>
       </c>
       <c r="E50" t="inlineStr">
+        <is>
+          <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>"Your path ahead (from your Plan)" renamed "Your retirement plan" (founder wording)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pair-mock round v7</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4251,6 +4251,33 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>Founder (chat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Plan (hub) + Net worth</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Retirement verdict wording: working = "Likely — retire at {65} with ~{pot at retirement}, lasting past {92} with ~{leftover} to spare"; retired = "Holding — on course to last past {92}, ~{leftover} to spare". Sentence only shown at 80%+ chance; numbers = median of the same simulation the odds use (never re-derived). Replaces "on course for ~$890,000 by 92".</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Founder read "by 92" as "working till 92" — ambiguous; workers act on the retirement-day pot first, survival second. 92 = plan-to age, 65 = retirement age: both dials now named in the sentence.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Founder ("approve these words", chat 2026-08-04)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4278,6 +4278,87 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>Founder ("approve these words", chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Net worth (all screens)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BANDED SECTIONS ADOPTED: deep-green title bands (white caps) + light-green group sub-bands, per pair mock v18 ("I like this") — founder ordered the pattern applied to ALL screens; UX doc bumped to v1.2 with tokens #085041 / #DFF2E9.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Wayfinding for 55-70 eyes; contrast-safe band colors.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Net worth / Performance / engines</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION RULE: cash = cash only. Money-market funds → Stocks/ETFs; CDs/T-bills → Bonds &amp; CDs (any maturity). Supersedes money-market=cash and the build-34 #8 12-month CD split. Built same day across sync/import/capture/kind-map/glossary; CD interest = balance × stated rate.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Dividend/interest payers must sit inside the measured buckets or change/ROI math silently loses their income.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pair mock v19 refinements: collapsed counts on a quiet 2nd line; ≥16px air before number columns; donut labels one weight.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Founder walk feedback on v18.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4357,6 +4357,33 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>All five tabs</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Banded sections BUILT on the five tab screens (Home 4 · Plan 6 · Net worth 5 · Performance 3 · Cash flow 6 bands) via the ONE SectionBand component; totals ride the bands; capture-surface sections use the light sub-band. Detail screens (~25) queued next.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Founder order: apply the adopted band pattern to all screens.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4384,6 +4384,33 @@
         </is>
       </c>
       <c r="E56" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NW change PERCENT re-based onto cash + investments (denominator named on the line: "+0.5% on cash + investments"); dollar change stays full NW. Store now captures a daily cash+investments point (invDaily) beside the nw point; percent shows only once that history exists — never back-guessed. Helper investableChangePct pinned (8 tests) + 2 screen pins.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Founder: "calculating NW % on total is not meaningful — property increments are hand-captured." Percent must measure money that actually moves daily.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4411,6 +4411,33 @@
         </is>
       </c>
       <c r="E57" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>All screens (rule)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EMPTY-STATE RULE adopted: full layout with $0 values + the add door; retirement first-view = the ONE Home sample app-wide. NW final mock bumped to v2 (State C redrawn to the rule).</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Founder: "when we don't have data, still show a layout meaningful enough to move forward; don't re-invent and be inconsistent."</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4440,6 +4440,33 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Net worth + Performance</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Value-walk structure APPROVED for both walks: Beginning value → ＋Contributions → −Withdrawals → WEALTH GENERATED (light sub-band; rows: Dividends · Interest · Change in investment value) → Ending value. Founder-confirmed calls: NW sheet says "net worth" (home+debts have no market feed) and carries the extra "＋ Debt principal you paid" line so the walk always sums; Performance uses the exact "market value" labels. Mocks: networth-final-v6 (sheet) + performance-final-v2 (walk card).</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>One walk grammar everywhere; rows must sum exactly to the ending value.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Founder ("agree with both", chat 2026-08-04)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4467,6 +4467,33 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>Founder ("agree with both", chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Income · Net worth · Performance</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FIFTH INGREDIENT CHECK built: each connected/imported account records how far back its source's activity feed reaches (history_from, recorded at ingest from the rows' own dates; depth only ever deepens). historyCoverage() turns a shortfall into one plain sentence ("E*TRADE shared 3 months of history (from May 4, 2026) — figures before that aren't counted"); silent when fully covered. Wired to the Income screen's 12-month investment-income figure; joins the four existing banner triggers. Also confirms the window rule: walk/return figures count ONLY rows dated inside the window (pre-join back-fill never leaks in), while income counts any dated receipt the broker vouches for.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Founder: brokers back-fill different depths, so a "past year" income figure can silently understate. Returns start when we start watching; income counts dated receipts.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Founder ("makes sense. Let's do it.", chat 2026-08-04)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4494,6 +4494,33 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>Founder ("makes sense. Let's do it.", chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Net worth (change sheet + banner)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Scoping rule for the depth sentence: it appears ONLY where the figure's window predates the source's shared history (12-month income yes; a 1-day change line no) — otherwise it implies older income sits inside the change number. Pinned. Walk sheet: all numbers share one right edge (WEALTH GENERATED total included); ＋ signs dropped, − kept. Mock networth-final-v8.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Founder: the history line "should only appear if the since-date is older than the shared history — otherwise the user thinks older dividends are added to the change number."</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4519,6 +4519,33 @@
         </is>
       </c>
       <c r="E61" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CONSISTENCY SWEEP: every fontSize snapped to the ONE design scale (11/13/15/17/20/24/30/38 — ties rounded UP for 55-70 readability): 622 values across 70 files. Hardcoded white/#F5F5F5 replaced with theme tokens in 42 files. Two guard tests added so drift cannot return.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Founder: "make sure font size and color and overall design are same across all screens."</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4546,6 +4546,33 @@
         </is>
       </c>
       <c r="E62" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Net worth</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FINAL design BUILT (part 1): three uber-groups (Cash · Investments · Personal property) as collapsible light-green bars carrying totals, with asset classes as rows inside; class donut returned to the screen (validated palette, direct-labeled legend, 44pt targets, masks with hide-balances); Own − Owe moved ABOVE the hero and the duplicate bottom math line removed; pills trimmed to two (By category · By institution — By type removed). Finding-14 cash-merge rule re-pinned on the class view.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Founder: "build all the approved NW".</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4573,6 +4573,33 @@
         </is>
       </c>
       <c r="E63" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Net worth (+ engine)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MISSING-DATA BANNER + FIX-IT SHEET BUILT: new dataGaps engine (5 checks — unpriced holding · stale connection · no dividend records · stale hand-entered value · shared-history depth) feeding an INLINE banner (never a pop-up) that counts and names each gap; tapping opens the sheet where each row states what is missing, what we do meanwhile, and a button landing on the exact cure. Renders nothing when data is complete. 7 engine pins + 1 screen pin.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Founder disclaimer rule: say nothing when complete; speak only when a promised number is missing an input.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4600,6 +4600,33 @@
         </is>
       </c>
       <c r="E64" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Net worth (change tap)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CHANGE WALK SHEET BUILT (final mock State E): tapping the change opens the walk in the approved structure — Beginning net worth → Contributions → Withdrawals → Wealth generated (Dividends · Interest · Change in investment value) → Debt principal you paid → Ending net worth. buildChangeWalk engine makes the rows sum to the ending value by construction (residual lands in change-in-value, never dropped). 3 engine pins + 1 screen pin. NET-WORTH FINAL IS NOW COMPLETE: 6 of 6 approved elements built.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Founder-approved walk structure + "design it exactly as the Performance walk card".</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4627,6 +4627,33 @@
         </is>
       </c>
       <c r="E65" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FINAL design part 1 BUILT: SUMMARY trio (ending value · wealth generated · return) with the plain window sentence ("for the window you picked — not a yearly rate; money you added never counts as return"); the VALUE WALK card in the approved order (beginning market value → contributions → withdrawals → wealth generated (dividends · interest · change in investment value) → ending market value), rows summing by construction via buildChangeWalk; missing-data banner below the summary. The old inline return-breakdown block was REMOVED — superseded by the walk (one concept, one place). One periodStartKey definition now feeds the walk, the ledger filter and the gap checks.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Founder final Performance spec + banner-below-summary instruction.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4654,6 +4654,33 @@
         </is>
       </c>
       <c r="E66" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Performance + Account page</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FINAL design part 2 BUILT: period chips carry their OWN window return (em-dash when a window has no data, row wraps to two lines); category-earnings table (CATEGORY | EARNED | RETURN, ledger-only, absent entirely when nothing was received). ACCOUNT PAGE restructured to the final mock: holdings grouped under their CLASS on the light-green sub-band ("BY CATEGORY &amp; HOLDING"), each holding carrying its own income line beneath it (income belongs to the holding that earned it), and every kind of record has a door — money in/out, income received, buy/sale — tightened per class (property keeps none; cash gains an interest door it never had).</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Founder final Performance spec incl. "income below individual asset", "class sub-bands", "missing button to add sales/buy transaction".</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4683,6 +4683,33 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Performance + NW family</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PERFORMANCE COMPLETE: per-account collapsible walks added (same engine as the all-accounts walk; collapsed by default with a one-line wealth-generated summary, expanding to the full walk; hidden when only one account exists). NW-family sub-screens banded (Import holdings, Bonds &amp; CDs, Alternatives, SnapTrade connect). 7 of 7 Performance elements and 6 of 6 Net-worth elements now built.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Founder: "complete fully building NW and perf section".</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-10)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5007,6 +5007,60 @@
       <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Claude (found + fixed 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (hero)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>TODAY'S DATE RETURNS TO THE HERO TITLE BAR (founder ask): the band reads "YOUR NET WORTH · AUG 11, 2026 ⓘ" and stamps the day these numbers are true as of. It does NOT replace the since-line: that names the day the CHANGE is measured from ("since Aug 3, 2026"), which is a different fact. One helper defines today, so the screen can never print two different todays, and a test asserts today appears exactly ONCE. The first-day screen keeps the bare title — dating a screen of zeros would imply something was measured today, and approved State C shows the title with its dot alone.</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-11 ('add today's date to the Net Worth hero box title bar'). Supersedes note 1 of 2026-08-10, which had taken the date off the title.</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (all section titles)</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>ONE TITLING TREATMENT FOR THE WHOLE SCREEN (founder ask): the hero and the retirement plan left their floating cards and now wear the SAME full-width deep-green banner as WHAT YOU OWN, WHAT YOU OWE and EMERGENCY CUSHION — five sections, one bar, each flush to both screen edges with the same 12pt text inset. Their bodies carry the ledger's own inset, so text under a banner lines up with rows under one. Applied to the first-day screen as well, so the treatment does not depend on having data. An appearance test measures all five RENDERED banners: same deep green, same stretch, same inset, no side margins, white caps.</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-11: "make hero box and retirement plan title Green Banner - across the screen (similar to what you own title bar). That would look better and consistent."</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5059,6 +5059,33 @@
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>BUILD 50 CUT (v1.1.0 build 50, from commit 8e09374 on taxonomy-v1.0.7) after the founder's explicit "cut the build" to a presented pre-build checklist. Gate satisfied in order: scope complete (59 of 59 tracker rows), audits FINISHED (mock-match audit round 1+2, and the 9-row open-gaps ledger re-verified against the live code and closed with the test that pins each), adversarial journey pass green (4 suites / 64 tests), then the checklist. Fresh gates at the cut: 1,492 tests green, tsc clean, UI-test gate passing, clean tree. Contents: the Net worth Quiet-Instrument rebuild, the founder's 11 hero corrections, his 6 audit decisions, the dated hero title, the one-banner titling, and 6 defects found during the audit (2 dead routes among them). Walk sheet: docs/FCC-core-55-70/build50-founder-walk-2026-08-11.xlsx.</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "cut the build" (2026-08-11), replying to the pre-build checklist.</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>BUILD 50 CUT (v1.1.0 build 50, from commit 8e09374 on taxonomy-v1.0.7) after the founder's explicit "cut the build" to a presented pre-build checklist. Gate satisfied in order: scope complete (59 of 59 tracker rows), audits FINISHED (mock-match audit round 1+2, and the 9-row open-gaps ledger re-verified against the live code and closed with the test that pins each), adversarial journey pass green (4 suites / 64 tests), then the checklist. Fresh gates at the cut: 1,492 tests green, tsc clean, UI-test gate passing, clean tree. Contents: the Net worth Quiet-Instrument rebuild, the founder's 11 hero corrections, his 6 audit decisions, the dated hero title, the one-banner titling, and 6 defects found during the audit (2 dead routes among them). Walk sheet: docs/FCC-core-55-70/build50-founder-walk-2026-08-11.xlsx.</t>
+          <t>BUILD 51 CUT (v1.1.0 build 51, from commit 8e09374 on taxonomy-v1.0.7) after the founder's explicit "cut the build" to a presented pre-build checklist. Gate satisfied in order: scope complete (59 of 59 tracker rows), audits FINISHED (mock-match audit round 1+2, and the 9-row open-gaps ledger re-verified against the live code and closed with the test that pins each), adversarial journey pass green (4 suites / 64 tests), then the checklist. Fresh gates at the cut: 1,492 tests green, tsc clean, UI-test gate passing, clean tree. Contents: the Net worth Quiet-Instrument rebuild, the founder's 11 hero corrections, his 6 audit decisions, the dated hero title, the one-banner titling, and 6 defects found during the audit (2 dead routes among them). Walk sheet: docs/FCC-core-55-70/build51-founder-walk-2026-08-11.xlsx. NUMBER CORRECTION 2026-08-11: this was first reported as build 50. `eas build:version:get` returns the LAST USED build number (50), not the next one; with autoIncrement the cut took 51. Build 50 is the Aug-10 build (commit 58bd1d1) and contains none of this work — which is why the founder saw no change on the Net worth screen when TestFlight showed 50. Read the number as the NEXT one from now on, or read it off the finished build.</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5086,6 +5086,114 @@
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>All screens (section titles)</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>GREEN TITLE BARS ARE SQUARE (founder ask): the rounded top corners are gone from SectionBand, so every green section title across the app is a straight edge-to-edge rule rather than a card lid. One component change, so it lands on all 29+ banded screens at once; a rendered-style test pins all four corners at 0.</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-11: "the green title bars are curved in the corners at the top. make them square and implement this on all screens."</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>All screens (account naming)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>ONE ACCOUNT-NAMING RULE ADOPTED: "&lt;institution&gt; -&lt;last four&gt;" — e.g. "Vanguard -5738" — used EVERYWHERE an account is named (Net worth rows, account detail, the missing-data banner and its fix sheet). The broker's own wording is never shown when we have the digits, so "Vanguard Kamala Kavadia Brokerage" becomes "Vanguard -5738". Only real digits qualify: E*TRADE relays a scrambled identifier through SnapTrade, and its tail is never passed off as "your last four". Where no digits exist the previous institution+label name stands, since dropping it would make two accounts at one firm identical.</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11. Root cause it fixes: the missing-data banner printed "Vanguard last updated Aug 3" TWICE for two different accounts, because it named accounts by institution alone.</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (missing-data sheet)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>THE "SYNC NOW" BUTTON NOW SYNCS. It previously NAVIGATED to the account page — which has no sync control on it — so a button labelled "Sync now" synced nothing and the person was left on a page that could not help. It now runs the sync in place, shows "Syncing…", and reports the outcome in the sheet. Gaps carry an explicit action (sync / reconnect / navigate) so a label and its behaviour can never drift apart again.</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Founder device finding 2026-08-11: "when I click on sync now, it takes to account detail page ... yet numbers are not updated."</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Net worth + Performance (connection honesty)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>A DEAD CONNECTION CAN NOW SAY IT IS DEAD. Per-account sync failures were caught and only console-warned, so a broken connection and a healthy idle one looked identical — same "connected" label, same unchanging date. Failures are now recorded against the account (store.syncFailures, cleared on the next good sync) and surface as their own row: "We couldn't reach Vanguard -5738", with the honest meanwhile ("its numbers are the ones from Aug 3 — we don't guess at newer ones") and a RECONNECT button, which is the actual cure the approved State F mock called for. The unreachable row REPLACES the plain stale row, so one problem never prints twice.</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Founder device finding 2026-08-11: "it shows connected read only yet numbers are not updated. Is it connected or not?" — the app could not answer, which was the defect.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5194,6 +5194,33 @@
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>All screens (account naming) — REFINED</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>THE NAMING RULE REFINED BY THE FOUNDER AND RECORDED IN THE PRD: (1) TAXABLE accounts = institution + last four ("Vanguard -5738"); with no digits = institution + the account word ("Vanguard Brokerage", "Chase Checking", "Ally Savings"); duplicates get · 1 / · 2. (2) TAX-ADVANTAGED accounts = institution + wrapper + last four when available ("Vanguard Roth IRA -5738"), because the wrapper IS the tax treatment; without digits "Fidelity 401(k)". A kind that describes HOLDINGS (stocks_etf, crypto, fixed_income, options) names the ACCOUNT that holds them — Brokerage — via a new wrapperWord map, so the row never reads "Vanguard Stocks / ETFs". Saved to the master requirements file: PRD v1.1 Amendments tab + a new Sameness-contract row naming the canonical helper and its pinning test.</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11, refining the same-day first pass. It resolves the open question I raised: the wrapper carries the tax treatment, so it is compulsory exactly where tax treatment differs and optional where the digits already identify the account.</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5221,6 +5221,33 @@
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Net worth + Plan hub (retirement verdict)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>THE RETIREMENT CARD NO LONGER GOES QUIET WHEN THE NEWS IS BAD. onCourseSentence returned null below 80% odds, so both the Net worth card and the Plan hub fell back to a bare "See your plan ›" — the founder saw this on device and asked whether it was stale code. It was not: it was a deliberate gate that silenced the verdict exactly when it mattered. The verdict words themselves prove the design meant to speak in every case (Likely / Uncertain / Unlikely; Holding / Watch closely / Running short). The sentence now renders for EVERY computable plan, and the ending tells the truth: "lasting past 92 with ~$890,000 to spare" only when there IS something spare, otherwise "running short around age 84" — the age read from the band the simulation already produces (new shortfallAgeFromBand helper, wired on both screens). It stays silent only when there is genuinely nothing to say: no odds yet, or no projected pot.</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Founder device finding 2026-08-11: "Your retirement plan - it says See your plan. That is not what I approved. Is it stale code?" The approved card shows a verdict word plus the plan; a fallback that hides both was never approved.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5248,6 +5248,87 @@
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Retirement odds — assumptions</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>PORTFOLIO RISK IS NOW MEASURED, NOT GUESSED. The Monte Carlo used volatility = return × 1.7 (floored at 5%), a rule of thumb that called a savings account 5% volatile and could not express that bonds and shares swing differently. New KIND_VOLATILITY table = the annual standard deviation of each asset kind, drawn from the SAME long-run series as the returns, each with a named source in VOLATILITY_META (S&amp;P 500 for shares, US Aggregate for bonds, T-bills for cash, Case-Shiller for property; crypto/PE/hedge flagged as estimates). blendedVolatility weights them the way the money actually sits — the same weighting blendedReturn uses — so the return and the risk always describe ONE portfolio. Weighted-average volatility assumes the parts move together, which slightly OVERSTATES risk; erring cautious rather than flattering is the right side. The old return×1.7 rule survives only as the scenario fallback, for when someone types a return on the Plan sliders with nothing held yet.</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Founder question 2026-08-11: "where are we getting data or assumptions for monte carlo simulation?" — I flagged the derived volatility as the weakest assumption and the founder asked for it to be fixed.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Retirement card (Net worth + Plan hub) — missing data</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>SAMPLE + ASK, IN EVERY PARTIAL CASE (founder rule). The verdict needs three answers — your age, what you spend, and what you have earmarked for retirement. Missing ANY of them used to produce a bare "See your plan ›", so someone missing one answer got LESS help than someone missing all three (the first-day screen already showed the labelled sample plus "3 answers make it yours"). Now any missing answer shows THE one app-wide sample ("Sample: 84% odds of lasting to age 90", always labelled) and names exactly what is missing: one → "add what you spend and it becomes yours"; two or three → "N answers make it yours: …". The sample figure and a real verdict never mix. SAMPLE_CHANCE/SAMPLE_HORIZON are now one constant so Home and Net worth cannot drift to two different samples.</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11, after asking what the must-have data points are and what should happen when one, two or all are missing.</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Retirement card — the info dot</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>THE ⓘ NOW EXPLAINS THE WHOLE METHOD IN PLAIN ENGLISH, for someone who does not follow finance: what we run (your retirement played out 500 times, counting how often the money lasts), what "Monte Carlo" means (named after the casino — roll the dice repeatedly and look at the spread; one tidy forecast would hide the risk), every assumption in the model (growth from what you actually hold with its named yardsticks, the year-to-year swing, 2.5% inflation, your spending/retirement age/horizon, Social Security from the claim age, required withdrawals and their tax from 73, big one-off costs in their year), WHERE TO CHANGE THEM (Plan tab → Retirement), and the two honest limits (each year's luck treated as independent though bad years cluster; holdings treated as moving together, which makes the odds cautious).</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-11: "update info dot for retirement plan to explain all this in plain english for someone who does not understand finances."</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5329,6 +5329,33 @@
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Retirement odds — the write-up + the master record</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>THE ACTUAL NUMBERS ADDED TO THE INFO DOT (founder ask): the write-up no longer names only the CATEGORIES of assumption but every figure — shares 10.4% (S&amp;P 500, 30 years), a 60/40 retirement mix 7.9%, brokerage 8%, bonds and CDs 4.2%, savings 2.4%, checking 0.5%, gold 8.2%, private equity 13%, crypto 8% (no long-run record — set your own), home 4.5%, car −5%; the year-to-year swings (shares ±18%, 60/40 ±11%, bonds ±6%, cash ±1%, crypto ±70%); inflation 2.5%; retire at 65 and plan to 90 unless answered; Social Security from the claim age (67 default); required-withdrawal tax 22% from age 73; big one-off costs in their stated year; and that the dice are SEEDED so the odds never jitter between visits. AND SAVED TO THE MASTER PRD: new tab "Retirement odds — assumptions" (45 rows) recording every input, its value, its source, whether the user can change it, and the code that owns it — with the two honest limits (independent yearly draws vs real clustering; weighted-average volatility ignoring diversification) written down rather than left implicit. An Amendments row dates the change in the PRD's own log.</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-11: "to the write add - assumption we are using. Again save all this in the master PRD file."</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5356,6 +5356,87 @@
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (composition bar)</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>THE BAR FOLLOWS THE TOGGLE. It stayed grouped by category even on the By-institution tab, so the picture and the list beneath it answered different questions. It now regroups by institution — the same money, biggest first, in the same order as the rows below — using the validated categorical palette. The spoken label changes with it ("What you own by institution: Vanguard 80 percent, Chase 20 percent").</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Founder device finding 2026-08-11: "What you own bar - does not change to institution when I toggle to institution from category."</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (account sub-line)</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>THE SUB-LINE COUNTS INSTEAD OF REPEATING. Under an account it read "CDs &amp; Treasuries in this account" — directly beneath a row already titled Bonds &amp; CDs. It now counts what is actually held: "3 CDs &amp; 1 Treasury in this account", singular/plural correct. Cash says plainly "cash in this account" (one account, one cash line) unless a money-market fund is present, which is named and counted. Shares and funds are counted as "N holdings in this account" — a bare ticker cannot tell a share from an ETF, and inventing that split would be a guess.</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: the line "seems repetitive as it is already listed under CDs and Bonds asset class... can we add the number and say 3 CD &amp; 1 treasury bond in this account?"</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (debt bar colours) — accessibility</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>THE DEBT BAR IS NOW READABLE WITHOUT COLOUR VISION. It alternated red and amber — the exact pair red-green colour blindness collapses into one muddy tone. New DebtRamp token: ONE hue in four clearly separated LIGHTNESS steps (#4A2E00 → #854F0B → #B98A4B → #E8CFA6), each adjacent pair &gt;1.7:1 in relative luminance, so the segments are told apart by light-vs-dark rather than hue — the same for protanopia, deuteranopia, tritanopia and a greyscale screenshot. Still in the warning family, so debts never look like assets, and every segment is still named with its percent in the legend. A test asserts the ramp is strictly increasing in lightness and contains no red.</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: "the colors for different types of debt not friendly for color blind people."</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5437,6 +5437,33 @@
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Asset classification — cash means cash ONLY (two more holes closed)</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>THE 2026-08-04 RULE NOW HOLDS AT THE LIVE CLASSIFICATION POINT, not only in the one-time migration. (a) accountClassBreakdown classified a POSITION purely by the tag the broker sends — and brokers tag both money-market funds and CDs as "cash" — so a holding synced AFTER the migration ran landed straight back in Cash. That is the founder's original CD-under-Cash defect mirrored in time (old data fixed, new data not). The name/ticker rule is applied at classification now, so it holds whenever the data arrives. (b) The rule matched on the fund NAME, so a broker sending only a symbol (VMFXX, SPAXX, SWVXX…) still put its money-market fund in Cash — the founder's own gap #2 surviving in the one place a name never appears. A list of the widely-held money-market symbols at Vanguard, Fidelity, Schwab, Merrill, BlackRock and Goldman now backs the name rule. ALSO: the account sub-line no longer names money-market funds under Cash at all — a cash slice is the sweep balance, so it reads "cash in this account". A stale 2026-07-19 test that asserted VMFXX belonged in Cash was corrected with the reason.</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Founder correction 2026-08-11: "we decided to move money markets and T-bills to stock/etf and bond &amp; CD respectively." Checking the copy against the rule exposed two places the rule was not actually being applied.</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5464,6 +5464,33 @@
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Net worth + all screens (money column)</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>ONE SIZE FOR EVERY MONEY FIGURE, AND A REAL RIGHT EDGE. (a) Band totals rendered at 13pt while row values rendered at 15pt; every money figure is 15pt now, totals bold, so a band total and the rows beneath it read as one column. SectionBand is shared, so this lands on every banded screen. (b) THE COLUMN WAS GENUINELY BENT, and the founder was right to doubt it: a ledger ROW lays out [name][gap 8][value][gap 8][arrow 16], so its value ends 36pt from the screen edge, while a BAND placed its total at padding + 16 = 28pt. Band totals sat 8 points right of every row value. One constant (RIGHT_SLOT = arrow + gap) is now what every band passes, so both end on the same line by construction. (c) The test that was supposed to guard this only asserted marginRight === 16 — necessary and not sufficient, and it never compared the two sides. It now COMPUTES the distance from the screen edge to each number's right edge and asserts equality, plus that every money figure is one size and totals are bold.</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11: "make all $$ same size and make totals bold. different size for dollar amount makes number not right aligned... are these tables or how are you ensuring they are right aligned?" — the question exposed a real 8-point misalignment and a test that could not have caught it.</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5491,6 +5491,33 @@
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Account detail — income attribution + activity order + the class slice</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>THREE DEFECTS THE FOUNDER FOUND ON ONE PAGE. (a) INCOME WAS GUESSED ONTO HOLDINGS: a ledger row with no ticker matched EVERY non-stock holding, so the whole account's untickered income was pinned onto each row — a CD read "$16,907 dividends", which a CD cannot pay, and two CDs showed the same figure twice. A holding now claims income only when the source names that holding; untickered income is still counted, at the ACCOUNT level in the Income figure, where it honestly belongs. (b) THE ACTIVITY LIST WAS UNSORTED and shows only the first eight rows, so on any account with history the dividends and interest could sit past the cut — the page appeared to have none while the figures above counted them. Newest first now, which is what made the page contradict itself. (c) THE CLASS SLICE SHOWED TWO BARE FIGURES ($224,190 above, $224,690 below) that read as a mismatch; the line now states the arithmetic — "$224,190 of $224,690 in Vanguard -5738 — the other $500 is Cash".</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Founder device findings 2026-08-11: "the top of the page says $224190, and below it says $224690 — source seems misaligned" and "activity does not list any dividend and interests, but the CD ticker says income: $16,907 dividends · $10,787 interest. What is the source — these numbers are not correct?"</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5518,6 +5518,33 @@
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Asset classification — the unexplained leftover</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>THE LEFTOVER IS CASH, NOT MORE OF THE BIGGEST HOLDING. When a broker's stated account total exceeded the sum of the holdings it itemised, the difference was added to the LARGEST class — so on a CD-heavy account the uninvested money was counted as MORE CDs, overstating the bonds slice and understating cash, silently, up to 1% of the account. A POSITIVE leftover is now cash: it is money the broker's total includes but its holdings do not account for — settlement cash, a dividend just received, a pending trade — and calling it cash is nearly always true, while calling it "more CDs" is a claim about what the person OWNS that we cannot support. A NEGATIVE leftover (priced holdings exceeding the stated total) stays absorbed by the largest class, because it is a pricing artifact rather than money and writing it into cash would show a negative cash balance. Totals still reconcile exactly either way.</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Founder question 2026-08-11: "why is cash added to CD and not cash?" — asked while checking the $500 difference on the Vanguard account page.</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5545,6 +5545,33 @@
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Transactions — a deposit into a holdings account</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>THE ROOT CAUSE BEHIND THE $500. A deposit only moves money into an account's cash sleeve when that account HAS one (derive_balance set, or a cash figure already present). The founder's Vanguard account itemises its holdings but its broker never sent a cash figure, so the deposit simply inflated the stated total — the holdings could no longer explain it, and the unexplained difference was then inferred elsewhere. That is the whole chain behind $500 of deposited money being counted as more CDs. Now: money arriving in an account that itemises holdings OPENS the cash sleeve and lands there, and the stated total rises by the same amount, so the classification explains the whole figure with nothing left to infer. A plain account with nothing to itemise is unchanged — it just grows, and no sleeve is invented. AND THE SCREEN SAYS SO: the deposit sheet now reads "Lands as cash in this account. When you invest it, record the purchase and it moves into that holding" (withdrawals get the matching sentence). It never needed to ASK — money arriving at a broker IS settlement cash until a purchase moves it — but it did need to say.</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: "$500 is what I added manually as a deposit to the Vanguard account. It never asked me if it was in cash or something else?"</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>
